--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_848_USA_West_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_848_USA_West_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5615d485e3ee4938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R15e8e92a30434884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd8617e5a1bf54758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7360432359b049b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbb05d47bc96349fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfe1b9d80ec5e4dad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc2f5c219dc554576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R056792e3c01e44c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfba9649c1f684bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb58f288aeb414afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R645b48df8b424b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rc92d7a6cc4194513"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ848CommercialTable" displayName="EEZ848CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ848CommercialTable" displayName="EEZ848CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ848FunctionalTable" displayName="EEZ848FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ848FunctionalTable" displayName="EEZ848FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ848ValidationTable" displayName="EEZ848ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ848ValidationTable" displayName="EEZ848ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13089,7 +13043,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R951858ff74ef409e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e6bc7ab07c14eef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13099,20 +13053,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13120,714 +13064,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>10164.8464966883</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.97</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>93.32543007969915</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>10164.8464966883</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>93.32543007969915</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$186,A2,'Species'!$U$2:$U$186))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>948638.6709975587</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.97</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>93.32543007969915</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>948638.6709975587</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>326098.6711577095</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.349882881164779</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2238.117490416719</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>326098.6711577095</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2238.32368647077</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$186,A3,'Species'!$U$2:$U$186))</x:f>
-        <x:v>729914379.7789438</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.349882881164779</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2238.117490416719</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>729847139.5197197</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>67240.2592240572</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000921292358127</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00009212923581272793</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>46800.80376562279</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.6684905317875156</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>466.11226600750814</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>46800.80376562279</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>647.656584661416</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$186,A4,'Species'!$U$2:$U$186))</x:f>
-        <x:v>30310848.726252392</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.6684905317875156</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>466.11226600750814</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>21814428.69416716</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>8496420.032085232</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3894862501880254</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.38948625018802546</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>11570.108528465396</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.606628762584005</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>404.23020567119016</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>11570.108528465396</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>683.3629267402525</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$186,A5,'Species'!$U$2:$U$186))</x:f>
-        <x:v>7906583.2267144695</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.606628762584005</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>404.23020567119016</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4676987.350099559</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3229595.8766149106</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.6905291023603393</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.6905291023603394</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2747.805709881</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.9979511523133344</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>99.5293464472577</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2747.805709881</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>120.72910002629422</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$186,A6,'Species'!$U$2:$U$186))</x:f>
-        <x:v>331740.11040104565</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.9979511523133344</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>99.5293464472577</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>273487.3064684989</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>58252.803932546754</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.2130000279894397</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.21300002798943976</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3307.8423241664</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.00668006169238</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.155003132156407</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3307.8423241664</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.165196729593841</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$186,A7,'Species'!$U$2:$U$186))</x:f>
-        <x:v>33624.86797562838</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.00668006169238</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.155003132156407</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>33591.149162589325</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>33.71881303905684</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0010038005212578</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0010038005212578346</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22468.970112248604</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6622848788887317</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>459.4993262066542</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22468.970112248604</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>580.5020811848069</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$186,A8,'Species'!$U$2:$U$186))</x:f>
-        <x:v>13043283.912239539</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6622848788887317</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>459.4993262066542</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10324476.627135685</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2718807.285103854</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2633360879483275</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.26333608794832747</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>5282.333732679899</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4351269830470073</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>272.34975131240435</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>5282.333732679899</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>307.10067471106765</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$186,A9,'Species'!$U$2:$U$186))</x:f>
-        <x:v>1622208.2533550295</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4351269830470073</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>272.34975131240435</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1438642.278444495</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>183565.97491053445</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.127596677548648</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12759667754864795</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>12627.101163515099</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.263642636912943</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1835.0277529826392</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>12627.101163515099</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2021.0839551619645</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$186,A10,'Species'!$U$2:$U$186))</x:f>
-        <x:v>25520431.56178734</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.263642636912943</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1835.0277529826392</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>23171081.074769583</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2349350.487017758</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1013914922414176</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1013914922414176</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>25123.143292813398</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7994228734551307</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>630.119432871192</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>25123.143292813398</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>729.1280365080927</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$186,A11,'Species'!$U$2:$U$186))</x:f>
-        <x:v>18317988.140000492</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7994228734551307</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>630.119432871192</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>15830580.803609269</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2487407.3363912236</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1571267262553064</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.1571267262553065</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1637.8090137047</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.864209495002772</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>731.4918554842599</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1637.8090137047</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>865.1037501881423</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$186,A12,'Species'!$U$2:$U$186))</x:f>
-        <x:v>1416874.7198478784</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.864209495002772</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>731.4918554842599</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1198043.9543636965</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>218830.76548418193</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.182656708618347</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.182656708618347</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>12412.619815964601</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.314744618299662</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2064.1659906184145</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>12412.619815964601</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2126.065136286783</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$186,A13,'Species'!$U$2:$U$186))</x:f>
-        <x:v>26390038.240704805</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.314744618299662</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2064.1659906184145</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>25621707.67859033</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>768330.5621144734</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0299874845093364</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.029987484509336415</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce8cad8b1d624d67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45e82df6b8c447c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13837,20 +13317,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13858,1362 +13328,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14895.073066403202</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8617003536496957</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>727.2778378841202</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14895.073066403202</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>728.3465451975821</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$186,A2,'Species'!$U$2:$U$186))</x:f>
-        <x:v>10848775.008380327</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8617003536496957</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>727.2778378841202</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>10832856.534859713</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>15918.473520614207</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0014694622299658</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.001469462229965769</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5731.2121213379005</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.829044138159578</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>674.5965847253124</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5731.2121213379005</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>679.4948289830674</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$186,A3,'Species'!$U$2:$U$186))</x:f>
-        <x:v>3894329.0002541794</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.829044138159578</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>674.5965847253124</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3866256.1233908604</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>28072.87686331896</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0072609977113203</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007260997711320255</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.0393640663</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.163269079927344</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1456.361132506365</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.0393640663</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1483.9994540811203</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$186,A4,'Species'!$U$2:$U$186))</x:f>
-        <x:v>58.41625289961303</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.163269079927344</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1456.361132506365</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>57.32829617672364</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1.0879567228893876</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.018977656679968</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.018977656679968074</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>7594.3425923398</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.292496703707947</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1961.0862907884514</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>7594.3425923398</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2187.8495974671387</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$186,A5,'Species'!$U$2:$U$186))</x:f>
-        <x:v>16615279.38367818</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.292496703707947</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1961.0862907884514</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>14893161.145388411</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1722118.2382897679</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1156314781985026</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.11563147819850272</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5237.0637797981</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.219251941930578</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1656.730783655648</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5237.0637797981</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1699.2810865970987</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$186,A6,'Species'!$U$2:$U$186))</x:f>
-        <x:v>8899243.430313624</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.219251941930578</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1656.730783655648</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8676404.779959517</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>222838.65035410784</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0256832934845102</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.02568329348451025</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1294.3568564649</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.2542363545540764</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1795.7106342165396</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1294.3568564649</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1945.8203915845143</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$186,A7,'Species'!$U$2:$U$186))</x:f>
-        <x:v>2518585.9652966326</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.2542363545540764</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1795.7106342165396</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2324290.371625112</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>194295.5936715207</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0835935113974904</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.08359351139749027</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>12474.901683691702</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.315192434048956</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2066.295519808177</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>12474.901683691702</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2128.244482852377</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$186,A8,'Species'!$U$2:$U$186))</x:f>
-        <x:v>26549640.682442695</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.315192434048956</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2066.295519808177</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>25776833.459059644</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>772807.2233830504</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0299806888464587</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.029980688846458603</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>856.3694780873</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.806264809781202</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>640.1250308625093</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>856.3694780873</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>649.0421394040816</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$186,A9,'Species'!$U$2:$U$186))</x:f>
-        <x:v>555819.8781781379</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.806264809781202</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>640.1250308625093</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>548183.5385903439</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7636.339587794035</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.013930260670415</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.01393026067041508</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>903.1884187102999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7902094210513178</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>616.8924017072102</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>903.1884187102999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>616.9572094482755</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$186,A10,'Species'!$U$2:$U$186))</x:f>
-        <x:v>557228.6064135073</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7902094210513178</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>616.8924017072102</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>557170.0728123343</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>58.53360117296688</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0001050551779953</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00010505517799532305</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>477.43024415680014</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.032359962978691</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1077.3578067180492</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>477.43024415680014</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1429.5505308831655</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$186,A11,'Species'!$U$2:$U$186))</x:f>
-        <x:v>682510.658994033</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.032359962978691</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1077.3578067180492</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>514363.2007056329</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>168147.45828840008</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.326904137111142</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.326904137111142</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>28311.066497628603</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.967998690079773</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>928.9635848331566</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>28311.066497628603</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>962.4909309565166</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$186,A12,'Species'!$U$2:$U$186))</x:f>
-        <x:v>27249144.749674402</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.967998690079773</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>928.9635848331566</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>26299949.824086946</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>949194.9255874567</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.036091130665129</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.03609113066512894</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1115.9899059637003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5732743912737988</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>374.3470294897616</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1115.9899059637003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>392.8928071791147</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$186,A13,'Species'!$U$2:$U$186))</x:f>
-        <x:v>438464.40693763446</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5732743912737988</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>374.3470294897616</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>417767.5062380696</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>20696.900699564838</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.049541671840247</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.049541671840247124</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>326006.8263254997</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.349889425319635</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>2238.1512156847193</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>326006.8263254997</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>2238.4714142600274</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$186,A14,'Species'!$U$2:$U$186))</x:f>
-        <x:v>729756961.5832645</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.349889425319635</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>2238.1512156847193</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>729652574.6619343</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>104386.92133021355</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.000143063870334</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.00014306387033387574</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>9993.082676504102</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.4538549461811736</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>284.35112196020793</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>9993.082676504102</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>479.1895413397476</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$186,A15,'Species'!$U$2:$U$186))</x:f>
-        <x:v>4788580.704324178</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.4538549461811736</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>284.35112196020793</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2841544.270905059</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1947036.4334191196</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.685203624435867</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.685203624435867</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>17218.600557725003</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.507820479995396</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>321.9737605157823</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>17218.600557725003</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>375.4118029302765</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$186,A16,'Species'!$U$2:$U$186))</x:f>
-        <x:v>6464065.879311808</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.507820479995396</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>321.9737605157823</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5543937.572389866</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>920128.3069219422</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1659701782185286</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.16597017821852847</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>4887.132431833101</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.0631138999255745</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>1156.4154888898177</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>4887.132431833101</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1281.9776829576886</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$186,A17,'Species'!$U$2:$U$186))</x:f>
-        <x:v>6265194.711268772</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.0631138999255745</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>1156.4154888898177</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>5651555.640427559</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>613639.0708412137</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.1085787896082342</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.10857878960823429</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>3815.3424829240003</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0190930714597415</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.449441319331317</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>3815.3424829240003</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.48763423420319</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$186,A18,'Species'!$U$2:$U$186))</x:f>
-        <x:v>40013.916439123546</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0190930714597415</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.449441319331317</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>39868.197388466186</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>145.71905065736064</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0036550197952896</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0036550197952896902</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>18489.737267994195</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2098904303857343</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>162.1400977050789</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>18489.737267994195</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>165.58937167148443</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$186,A19,'Species'!$U$2:$U$186))</x:f>
-        <x:v>3061703.976577988</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2098904303857343</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>162.1400977050789</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2997927.807173817</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>63776.16940417094</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0212734173423255</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.02127341734232537</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.0081370191</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.62</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>416.8693834703355</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.0081370191</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$186,A20,'Species'!$U$2:$U$186))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>3.392074135503344</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.62</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>416.8693834703355</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>3.392074135503344</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>7.2155084399</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.3270399442632628</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>212.34397565288947</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>7.2155084399</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>212.84815126022977</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$186,A21,'Species'!$U$2:$U$186))</x:f>
-        <x:v>1535.8076318352996</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.3270399442632628</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>212.34397565288947</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1532.1697484853441</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>3.637883349955473</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0023743344061922</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0023743344061921156</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>10357.7812424365</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>2.9790151265540503</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>95.28293506614585</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>10357.7812424365</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>96.90015359682894</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$186,A22,'Species'!$U$2:$U$186))</x:f>
-        <x:v>1003670.5933144506</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>2.9790151265540503</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>95.28293506614585</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>986919.7975524205</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>16750.79576203006</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0169728034674879</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.01697280346748778</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>10271.285182974898</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.5251950288103533</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>335.11589601243617</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>10271.285182974898</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>524.4996297494372</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$186,A23,'Species'!$U$2:$U$186))</x:f>
-        <x:v>5387285.275521214</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.5251950288103533</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>335.11589601243617</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>3442070.9372918922</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>1945214.3382293219</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.5651290672584894</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.5651290672584895</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>302.6095037420001</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.7642118881699154</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>581.047836120424</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>302.6095037420001</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>588.2564692342459</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$186,A24,'Species'!$U$2:$U$186))</x:f>
-        <x:v>178011.99822799626</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.7642118881699154</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>581.047836120424</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>175830.5973387645</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>2181.400889231765</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0124062644513967</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.012406264451396722</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1.3997877186</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.5800000000000005</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>380.1893963205616</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1.3997877186</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$186,A25,'Species'!$U$2:$U$186))</x:f>
-        <x:v>532.1844477114697</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.5800000000000005</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>380.1893963205616</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>532.1844477114702</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>-4.547473508864641e-13</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>-8.544919958521798e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35be2221f9a40e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d9edbadcfd74611"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15388,7 +13974,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15487,7 +14073,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>855756640.2092198</x:v>
+        <x:v>835178805.1075281</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15501,7 +14087,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>855756640.2092198</x:v>
+        <x:v>846041591.1136853</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15515,7 +14101,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-4.76837158203125e-7</x:v>
+        <x:v>-20577835.1016922</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15529,7 +14115,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-4.76837158203125e-7</x:v>
+        <x:v>-9715049.09553504</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15540,9 +14126,9 @@
         <x:v>EEZ_848</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15554,47 +14140,19 @@
         <x:v>EEZ_848</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_848</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_848</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d16d4da9ca64d17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2f72c3541454779"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15641,7 +14199,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
